--- a/文件夹/需求/线下商超退货/方案/线下商超退货-对账单导入模板.xlsx
+++ b/文件夹/需求/线下商超退货/方案/线下商超退货-对账单导入模板.xlsx
@@ -490,94 +490,88 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>线下商超退货 · 对账单/凭证导入模板（明细行从第 5 行起填；第 3～4 行为表头与说明）｜批次级「销售组织、客户 KA、退货类型」在系统导入向导中选择，字典见 Sheet「字典值」</t>
+          <t>线下商超退货 · 对账单/凭证导入模板（明细行从第 5 行起填）｜批次级「销售组织、客户 KA、退货类型」在系统导入向导中选择，字典见 Sheet「字典值」</t>
         </is>
       </c>
     </row>
     <row r="2" ht="28" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>带 * 为必填；店铺 / Sales / 物流 / 财务 / 处理方式 请从「字典值」工作表取值，勿自造字段。</t>
+          <t>带 * 为必填；店铺 / Sales / 物流 / 财务 / 处理方式 请从「字典值」工作表取值。</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>客户产品编码*</t>
+          <t>店铺*</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>店铺*</t>
+          <t>Sales*</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Sales*</t>
+          <t>物流*</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>物流*</t>
+          <t>财务*</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>财务*</t>
+          <t>MSKU*</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>MSKU*</t>
+          <t>数量*</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>数量*</t>
+          <t>单价*</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>单价*</t>
+          <t>手续费单价</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>手续费单价</t>
+          <t>退货月份起</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>退货月份起</t>
+          <t>退货月份止</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>退货月份止</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
         <is>
           <t>处理方式*</t>
         </is>
@@ -586,60 +580,55 @@
     <row r="4" ht="48" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>必填：客户系统原始编码，如 Costco PN、沃尔玛 Item #</t>
+          <t>必填：须为字典「店铺」中的值</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>必填：须为字典「店铺」中的值</t>
+          <t>必填：须为字典「Sales人员」；该步骤待办通知此人</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>必填：须为字典「Sales人员」中的姓名；该步骤待办通知此人</t>
+          <t>必填：须为字典「物流人员」中的姓名</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>必填：须为字典「物流人员」中的姓名</t>
+          <t>必填：须为字典「财务人员」中的姓名</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>必填：须为字典「财务人员」中的姓名</t>
+          <t>必填：8 位生产 SKU；须已在销售主数据维护</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>必填：8 位生产 SKU；须已在销售主数据维护</t>
+          <t>必填：整数，≥0</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>必填：整数，≥0</t>
+          <t>必填：客户对账单价，小数</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>必填：客户对账单价，小数</t>
+          <t>选填：如沃尔玛按 SKU 分摊手续费；无则填 0</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>选填：如沃尔玛按 SKU 分摊手续费；无则填 0</t>
+          <t>选填：格式 YYYY-MM，与「退货月份止」成对填写</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>选填：格式 YYYY-MM，与「退货月份止」成对填写</t>
+          <t>选填：格式 YYYY-MM</t>
         </is>
       </c>
       <c r="K4" s="4" t="inlineStr">
-        <is>
-          <t>选填：格式 YYYY-MM</t>
-        </is>
-      </c>
-      <c r="L4" s="4" t="inlineStr">
         <is>
           <t>条件必填：A-1/B 类必填；A-2 留空。须为字典「处理方式」</t>
         </is>
@@ -648,54 +637,49 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>B07XXXX-01</t>
+          <t>Govee_US</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Govee_US</t>
+          <t>王晓雨</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>王晓雨</t>
+          <t>刘仓储</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>刘仓储</t>
+          <t>孙会计</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>孙会计</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
           <t>H70501</t>
         </is>
       </c>
+      <c r="F5" t="n">
+        <v>12</v>
+      </c>
       <c r="G5" t="n">
-        <v>12</v>
+        <v>89.98999999999999</v>
       </c>
       <c r="H5" t="n">
-        <v>89.98999999999999</v>
-      </c>
-      <c r="I5" t="n">
         <v>0</v>
       </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
         <is>
           <t>返修上架</t>
         </is>
@@ -704,49 +688,44 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>WM-ITEM-9912</t>
+          <t>Govee_US</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Govee_US</t>
+          <t>陈思远</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>陈思远</t>
+          <t>周预报</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>周预报</t>
+          <t>钱核对</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>钱核对</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
           <t>H61234</t>
         </is>
       </c>
+      <c r="F6" t="n">
+        <v>20</v>
+      </c>
       <c r="G6" t="n">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="H6" t="n">
-        <v>45</v>
-      </c>
-      <c r="I6" t="n">
         <v>4.5</v>
       </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
-        <is>
-          <t>2025-12</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
         <is>
           <t>2026-01</t>
         </is>
@@ -755,54 +734,49 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SAM-BULK-01</t>
+          <t>Govee_US</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Govee_US</t>
+          <t>赵一帆</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>赵一帆</t>
+          <t>吴物流</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>吴物流</t>
+          <t>郑金蝶</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>郑金蝶</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
           <t>H61200</t>
         </is>
       </c>
+      <c r="F7" t="n">
+        <v>200</v>
+      </c>
       <c r="G7" t="n">
-        <v>200</v>
+        <v>32.5</v>
       </c>
       <c r="H7" t="n">
-        <v>32.5</v>
-      </c>
-      <c r="I7" t="n">
         <v>0</v>
       </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
           <t>2026-03</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
-        <is>
-          <t>2026-03</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
         <is>
           <t>原箱上架</t>
         </is>
@@ -810,23 +784,23 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:L2"/>
-    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A1:K1"/>
   </mergeCells>
   <dataValidations count="5">
-    <dataValidation sqref="B5:B5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值不在字典范围内" error="请从字典值工作表中选择或填写完全一致的值" promptTitle="字典字段" prompt="请从下拉选择，或参照 Sheet「字典值」" type="list">
+    <dataValidation sqref="A5:A5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值不在字典范围内" error="请从字典值工作表中选择或填写完全一致的值" promptTitle="字典字段" prompt="请从下拉选择，或参照 Sheet「字典值」" type="list">
       <formula1>=字典值!$D$3:$D$16</formula1>
     </dataValidation>
-    <dataValidation sqref="C5:C5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值不在字典范围内" error="请从字典值工作表中选择或填写完全一致的值" promptTitle="字典字段" prompt="请从下拉选择，或参照 Sheet「字典值」" type="list">
+    <dataValidation sqref="B5:B5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值不在字典范围内" error="请从字典值工作表中选择或填写完全一致的值" promptTitle="字典字段" prompt="请从下拉选择，或参照 Sheet「字典值」" type="list">
       <formula1>=字典值!$E$3:$E$6</formula1>
     </dataValidation>
-    <dataValidation sqref="D5:D5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值不在字典范围内" error="请从字典值工作表中选择或填写完全一致的值" promptTitle="字典字段" prompt="请从下拉选择，或参照 Sheet「字典值」" type="list">
+    <dataValidation sqref="C5:C5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值不在字典范围内" error="请从字典值工作表中选择或填写完全一致的值" promptTitle="字典字段" prompt="请从下拉选择，或参照 Sheet「字典值」" type="list">
       <formula1>=字典值!$F$3:$F$6</formula1>
     </dataValidation>
-    <dataValidation sqref="E5:E5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值不在字典范围内" error="请从字典值工作表中选择或填写完全一致的值" promptTitle="字典字段" prompt="请从下拉选择，或参照 Sheet「字典值」" type="list">
+    <dataValidation sqref="D5:D5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值不在字典范围内" error="请从字典值工作表中选择或填写完全一致的值" promptTitle="字典字段" prompt="请从下拉选择，或参照 Sheet「字典值」" type="list">
       <formula1>=字典值!$G$3:$G$6</formula1>
     </dataValidation>
-    <dataValidation sqref="L5:L5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值不在字典范围内" error="请从字典值工作表中选择或填写完全一致的值" promptTitle="字典字段" prompt="请从下拉选择，或参照 Sheet「字典值」" type="list">
+    <dataValidation sqref="K5:K5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值不在字典范围内" error="请从字典值工作表中选择或填写完全一致的值" promptTitle="字典字段" prompt="请从下拉选择，或参照 Sheet「字典值」" type="list">
       <formula1>=字典值!$H$3:$H$6</formula1>
     </dataValidation>
   </dataValidations>
@@ -857,7 +831,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>本页为导入允许取值；「导入明细」中带下拉或需手填一致的字段请参照此表。</t>
+          <t>本页为导入允许取值；「导入明细」中带下拉的字段请参照此表。</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1201,7 @@
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>4. MSKU 参考列为常用编码，实际以销售主数据为准；未映射行导入后会标黄待补。</t>
+          <t>4. MSKU 参考列为常用编码，实际以销售主数据为准；未维护行导入后会标黄待补。</t>
         </is>
       </c>
     </row>

--- a/文件夹/需求/线下商超退货/方案/线下商超退货-对账单导入模板.xlsx
+++ b/文件夹/需求/线下商超退货/方案/线下商超退货-对账单导入模板.xlsx
@@ -490,20 +490,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="8" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1">
@@ -513,10 +515,10 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="28" customHeight="1">
+    <row r="2" ht="32" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>带 * 为必填；店铺 / Sales / 物流 / 财务 / 处理方式 请从「字典值」工作表取值。</t>
+          <t>带 * 为必填；店铺 / Sales / 物流 / 财务 / 处理方式 请从「字典值」取值；订单/PO、invoice/PI 按客户单据填写。</t>
         </is>
       </c>
     </row>
@@ -543,35 +545,45 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
+          <t>订单/PO</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>invoice/PI</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
           <t>MSKU*</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>数量*</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>单价*</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>手续费单价</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>退货月份起</t>
         </is>
       </c>
-      <c r="J3" s="3" t="inlineStr">
+      <c r="L3" s="3" t="inlineStr">
         <is>
           <t>退货月份止</t>
         </is>
       </c>
-      <c r="K3" s="3" t="inlineStr">
+      <c r="M3" s="3" t="inlineStr">
         <is>
           <t>处理方式*</t>
         </is>
@@ -600,35 +612,45 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
+          <t>选填：客户采购订单号，与对账单/凭证一致</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>选填：客户发票或形式发票号</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
           <t>必填：8 位生产 SKU；须已在销售主数据维护</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>必填：整数，≥0</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="I4" s="4" t="inlineStr">
         <is>
           <t>必填：客户对账单价，小数</t>
         </is>
       </c>
-      <c r="H4" s="4" t="inlineStr">
+      <c r="J4" s="4" t="inlineStr">
         <is>
           <t>选填：如沃尔玛按 SKU 分摊手续费；无则填 0</t>
         </is>
       </c>
-      <c r="I4" s="4" t="inlineStr">
+      <c r="K4" s="4" t="inlineStr">
         <is>
           <t>选填：格式 YYYY-MM，与「退货月份止」成对填写</t>
         </is>
       </c>
-      <c r="J4" s="4" t="inlineStr">
+      <c r="L4" s="4" t="inlineStr">
         <is>
           <t>选填：格式 YYYY-MM</t>
         </is>
       </c>
-      <c r="K4" s="4" t="inlineStr">
+      <c r="M4" s="4" t="inlineStr">
         <is>
           <t>条件必填：A-1/B 类必填；A-2 留空。须为字典「处理方式」</t>
         </is>
@@ -657,29 +679,39 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
+          <t>PO-COS-2026-001</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>INV-COS-260526-01</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
           <t>H70501</t>
         </is>
       </c>
-      <c r="F5" t="n">
+      <c r="H5" t="n">
         <v>12</v>
       </c>
-      <c r="G5" t="n">
+      <c r="I5" t="n">
         <v>89.98999999999999</v>
       </c>
-      <c r="H5" t="n">
+      <c r="J5" t="n">
         <v>0</v>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>2026-01</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>2026-02</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>返修上架</t>
         </is>
@@ -708,24 +740,34 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
+          <t>WM-PO-9912</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>PI-WM-260525-01</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
           <t>H61234</t>
         </is>
       </c>
-      <c r="F6" t="n">
+      <c r="H6" t="n">
         <v>20</v>
       </c>
-      <c r="G6" t="n">
+      <c r="I6" t="n">
         <v>45</v>
       </c>
-      <c r="H6" t="n">
+      <c r="J6" t="n">
         <v>4.5</v>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>2025-12</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>2026-01</t>
         </is>
@@ -754,29 +796,39 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
+          <t>SAM-PO-BULK-01</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>PI-SAM-260524-01</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
           <t>H61200</t>
         </is>
       </c>
-      <c r="F7" t="n">
+      <c r="H7" t="n">
         <v>200</v>
       </c>
-      <c r="G7" t="n">
+      <c r="I7" t="n">
         <v>32.5</v>
       </c>
-      <c r="H7" t="n">
+      <c r="J7" t="n">
         <v>0</v>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>原箱上架</t>
         </is>
@@ -784,8 +836,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="A1:M1"/>
   </mergeCells>
   <dataValidations count="5">
     <dataValidation sqref="A5:A5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值不在字典范围内" error="请从字典值工作表中选择或填写完全一致的值" promptTitle="字典字段" prompt="请从下拉选择，或参照 Sheet「字典值」" type="list">
@@ -800,7 +852,7 @@
     <dataValidation sqref="D5:D5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值不在字典范围内" error="请从字典值工作表中选择或填写完全一致的值" promptTitle="字典字段" prompt="请从下拉选择，或参照 Sheet「字典值」" type="list">
       <formula1>=字典值!$G$3:$G$6</formula1>
     </dataValidation>
-    <dataValidation sqref="K5:K5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值不在字典范围内" error="请从字典值工作表中选择或填写完全一致的值" promptTitle="字典字段" prompt="请从下拉选择，或参照 Sheet「字典值」" type="list">
+    <dataValidation sqref="M5:M5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值不在字典范围内" error="请从字典值工作表中选择或填写完全一致的值" promptTitle="字典字段" prompt="请从下拉选择，或参照 Sheet「字典值」" type="list">
       <formula1>=字典值!$H$3:$H$6</formula1>
     </dataValidation>
   </dataValidations>
@@ -814,7 +866,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1187,34 +1239,42 @@
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>2. A-2（仅退款）行：「处理方式」列留空；A-1/B 须填处理方式。</t>
+          <t>2. 订单/PO、invoice/PI：分别填写客户采购订单号与发票/形式发票号，无则留空。</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="8" t="inlineStr">
         <is>
-          <t>3. 退款金额 = 数量×单价 + 数量×手续费单价（系统计算，无需导入列）。</t>
+          <t>3. A-2（仅退款）行：「处理方式」列留空；A-1/B 须填处理方式。</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>4. MSKU 参考列为常用编码，实际以销售主数据为准；未维护行导入后会标黄待补。</t>
+          <t>4. 退款金额 = 数量×单价 + 数量×手续费单价（系统计算，无需导入列）。</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="8" t="inlineStr">
         <is>
-          <t>5. 退货月份：填 YYYY-MM；起止可相同表示单月。</t>
+          <t>5. MSKU 参考列为常用编码，实际以销售主数据为准；未维护行导入后会标黄待补。</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>6. 退货月份：填 YYYY-MM；起止可相同表示单月。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="7">
     <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A25:I25"/>
     <mergeCell ref="A23:I23"/>
     <mergeCell ref="A24:I24"/>
     <mergeCell ref="A22:I22"/>
